--- a/documentation/Sprint 2 Backlog.xlsx
+++ b/documentation/Sprint 2 Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nginn1\Documents\GitHub\DevOps-Project-1\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{144B0CB5-E87D-4BE3-BD99-7B9DCE328B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADE85E1-1345-445F-9113-2CC7C1A31FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Related User Story</t>
   </si>
@@ -135,6 +135,15 @@
   </si>
   <si>
     <t>Update the series that was edited in the listview</t>
+  </si>
+  <si>
+    <t>Add a notes section for each series</t>
+  </si>
+  <si>
+    <t>Add a boolean setting for keeping track of owned and not owned series</t>
+  </si>
+  <si>
+    <t>Add filtering for owned series</t>
   </si>
 </sst>
 </file>
@@ -340,7 +349,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>11.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1577,7 +1586,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1607,7 +1616,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="1">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1675,7 +1684,9 @@
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="2"/>
@@ -1684,7 +1695,9 @@
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="2"/>
@@ -1693,7 +1706,9 @@
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2"/>
@@ -1717,7 +1732,7 @@
       </c>
       <c r="C23" s="3">
         <f>SUM(C3:C22)</f>
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(D3:D22)</f>

--- a/documentation/Sprint 2 Backlog.xlsx
+++ b/documentation/Sprint 2 Backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nginn1\Documents\GitHub\DevOps-Project-1\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ADE85E1-1345-445F-9113-2CC7C1A31FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D488D01-EDED-435D-A1C6-F177D01E5DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="2445" windowWidth="19860" windowHeight="8805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Related User Story</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Add filtering for owned series</t>
+  </si>
+  <si>
+    <t>/</t>
   </si>
 </sst>
 </file>
@@ -1468,7 +1471,9 @@
       <c r="C4" s="1">
         <v>0.5</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -1483,7 +1488,9 @@
       <c r="C5" s="1">
         <v>0.5</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1498,7 +1505,9 @@
       <c r="C6" s="1">
         <v>0.5</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
@@ -1513,7 +1522,9 @@
       <c r="C7" s="1">
         <v>0.5</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1528,7 +1539,9 @@
       <c r="C8" s="1">
         <v>0.5</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
